--- a/input/selectlist_ROE.xlsx
+++ b/input/selectlist_ROE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A622E0-FA4F-4648-9D30-9DEA9D487D5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CA4839-D41B-4A52-A40B-06810162D966}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" xr2:uid="{8EFC6329-1B1D-4247-998B-325220D9F705}"/>
   </bookViews>
@@ -126,12 +126,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -506,15 +507,15 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="3"/>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="3"/>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+      <c r="A10" s="3"/>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
